--- a/docs/audit/CHECKLIST-VALIDATION-V1.xlsx
+++ b/docs/audit/CHECKLIST-VALIDATION-V1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Commandes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commandes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J214"/>
+  <dimension ref="A1:J263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9153,13 +9153,2037 @@
         <v>60</v>
       </c>
     </row>
+    <row r="215" ht="32" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="45" customHeight="1">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>13.1 Migration auto au boot</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>13.1.2</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.mouvements.filter(m =&gt; m.pj &amp;&amp; m.pj.dataB64).length`</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>0 (toutes migrées)</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 0 → migration incomplète</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr"/>
+      <c r="I216" s="3" t="inlineStr"/>
+      <c r="J216" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" ht="45" customHeight="1">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>13.1 Migration auto au boot</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>13.1.3</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.documents.filter(d =&gt; d.parentType==='mouvement').length`</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>≥ N (au moins N PJ migrées dans DB.documents)</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>0 → migration n'a pas créé d'entrée</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr"/>
+      <c r="I217" s="3" t="inlineStr"/>
+      <c r="J217" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" ht="45" customHeight="1">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>13.1 Migration auto au boot</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.documents.filter(d =&gt; d._discoveredFromDrive).length`</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Nombre de fichiers découverts par Drive scan (peut être 0)</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr"/>
+      <c r="I218" s="3" t="inlineStr"/>
+      <c r="J218" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" ht="32" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>13.1 Migration auto au boot</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>13.1.5</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Réouvrir un mouvement avec PJ migrée → modale édition</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Champ PJ affiche le nom du document (binaire chargé lazy depuis IDB)</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>Visuel modale + console (IDB get)</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>Affiche 'binaire introuvable' → idbKey perdu</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr"/>
+      <c r="I219" s="3" t="inlineStr"/>
+      <c r="J219" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" ht="32" customHeight="1">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>13.2.1</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Ouvrir un mouvement existant → ajouter PJ 1 MB image</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Toast 'Mouvement enregistré' OK, pas de 'Stockage plein'</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>Toast 'Stockage plein' → bug régression Sprint 1</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr"/>
+      <c r="I220" s="3" t="inlineStr"/>
+      <c r="J220" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" ht="32" customHeight="1">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>13.2.2</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.mouvements.find(...).pjId`</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Number (id du DB.documents associé)</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>undefined → m.pjId pas écrit dans saveMv</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr"/>
+      <c r="I221" s="3" t="inlineStr"/>
+      <c r="J221" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" ht="32" customHeight="1">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>13.2.3</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.documents.find(d =&gt; d.id === ...).idbKey`</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>String 'ph_xxxxx' (clé IndexedDB)</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>null → IDB pas écrit</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr"/>
+      <c r="I222" s="3" t="inlineStr"/>
+      <c r="J222" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" ht="32" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>13.2.4</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Ajouter PJ 8 MB image</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Accept (limite 10 MB v14.99 vs 2 MB legacy)</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>Refus &lt; 10 MB → limite pas mise à jour</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr"/>
+      <c r="I223" s="3" t="inlineStr"/>
+      <c r="J223" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" ht="32" customHeight="1">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>13.2.5</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Ajouter PJ 11 MB</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Refus avec toast 'trop lourd'</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>Accepté &gt; 10 MB → validation cassée</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr"/>
+      <c r="I224" s="3" t="inlineStr"/>
+      <c r="J224" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" ht="32" customHeight="1">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>13.2.6</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Remplacer une PJ existante par une autre</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>Ancien attachement tombstone, IDB nettoyé, nouveau créé</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>Console (DB.documents, IDB)</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>Ancien toujours actif → fuite</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr"/>
+      <c r="I225" s="3" t="inlineStr"/>
+      <c r="J225" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" ht="32" customHeight="1">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>13.2.7</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Avec Drive connecté : ajouter PJ sur mvt logement</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>Toast OK + background upload Drive → log '[attachment Drive] uploadé' dans console</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>Console + Drive web</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>Pas d'upload Drive après 5s → background cassé</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr"/>
+      <c r="I226" s="3" t="inlineStr"/>
+      <c r="J226" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" ht="45" customHeight="1">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>13.2 Upload PJ mouvement</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>13.2.8</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Drive web : vérifier fichier dans ImmoTrack/&lt;ent&gt;/&lt;imm&gt;/&lt;log&gt;/📄 Documents/</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>Fichier nommé `documents_YYYY-MM-DD_nom.pdf`</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Drive web</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>Fichier absent → upload background échoué</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr"/>
+      <c r="I227" s="3" t="inlineStr"/>
+      <c r="J227" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" ht="32" customHeight="1">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>13.3 Sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>13.3.1</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Ouvrir fiche logement → sous-onglet 📁 Documents</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>Section '📎 Documents libres' visible en bas</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>Section absente → _renderAttachmentSection cassé</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr"/>
+      <c r="I228" s="3" t="inlineStr"/>
+      <c r="J228" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" ht="32" customHeight="1">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>13.3 Sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>13.3.2</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer '+ Ajouter' → uploader un PDF DPE</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>Toast '📎 PJ ajoutée : XXX.pdf' + apparaît dans la liste</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Visuel + toast</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>Erreur upload</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr"/>
+      <c r="I229" s="3" t="inlineStr"/>
+      <c r="J229" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" ht="45" customHeight="1">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>13.3 Sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>13.3.3</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Vérifier listing : icône 📄 + nom + taille + date + indicateurs ☁️💾</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Tous les éléments présents</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>Indicateurs absents</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr"/>
+      <c r="I230" s="3" t="inlineStr"/>
+      <c r="J230" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" ht="32" customHeight="1">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>13.3 Sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>13.3.4</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer 👁 Aperçu sur le DPE PDF</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>Nouvel onglet popup avec PDF lisible (iframe)</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>Popup + visuel</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>Pas de popup OU PDF blanc</t>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr"/>
+      <c r="I231" s="3" t="inlineStr"/>
+      <c r="J231" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" ht="32" customHeight="1">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>13.3 Sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>13.3.5</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer 🗑 sur un document</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>Confirm dialog + suppression réussie (tombstone DB + IDB del + Drive trash)</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>Confirm + visuel + console</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>Confirm absent OU document toujours visible après</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr"/>
+      <c r="I232" s="3" t="inlineStr"/>
+      <c r="J232" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" ht="32" customHeight="1">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>13.4.1</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Ouvrir fiche logement → sous-onglet 📷 Photos</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Affichage 'Aucune photo' si vide, sinon grid thumbnails</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>Page blanche / erreur JS</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr"/>
+      <c r="I233" s="3" t="inlineStr"/>
+      <c r="J233" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" ht="32" customHeight="1">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>13.4.2</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer '+ Ajouter photos' → uploader 3 photos JPG</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>Toast '📷 3 photo(s) ajoutée(s)' + grid se peuple</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Toast + visuel</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>Pas de toast OU grid vide</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr"/>
+      <c r="I234" s="3" t="inlineStr"/>
+      <c r="J234" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" ht="45" customHeight="1">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>13.4.3</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Vérifier grid responsive : `repeat(auto-fill, minmax(180px, 1fr))`</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>3 photos en 3 col PC, 2 col tablette, 1 col mobile</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Visuel responsive DevTools</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>Mauvais layout / pas responsive</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="inlineStr"/>
+      <c r="I235" s="3" t="inlineStr"/>
+      <c r="J235" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" ht="32" customHeight="1">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>13.4.4</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Vérifier que les thumbnails se chargent depuis IDB (lazy)</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Apparition progressive des images après le render</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Visuel + console (IDB get)</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>Images cassées / placeholder</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr"/>
+      <c r="I236" s="3" t="inlineStr"/>
+      <c r="J236" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" ht="32" customHeight="1">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>13.4.5</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer une photo → lightbox plein écran</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>Modale 92% opacité, image centrée, header avec nom/taille/index</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>Pas de lightbox</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr"/>
+      <c r="I237" s="3" t="inlineStr"/>
+      <c r="J237" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" ht="32" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>13.4.6</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Lightbox : appuyer ArrowRight + ArrowLeft + Escape</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>Navigation prev/next + close OK</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>Visuel + keyboard</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>Touches inopérantes</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr"/>
+      <c r="I238" s="3" t="inlineStr"/>
+      <c r="J238" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" ht="32" customHeight="1">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>13.4.7</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer ☆ sur une photo (toggle cover)</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>Badge ⭐ Couverture apparaît + bordure colorée</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>Pas de feedback visuel</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr"/>
+      <c r="I239" s="3" t="inlineStr"/>
+      <c r="J239" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" ht="32" customHeight="1">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>13.4.8</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer ⭐ sur la même photo (toggle off)</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>Badge ⭐ disparaît</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>Cover ne se retire pas</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr"/>
+      <c r="I240" s="3" t="inlineStr"/>
+      <c r="J240" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" ht="32" customHeight="1">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>13.4.9</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer ⭐ sur photo A, puis sur photo B</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>Photo B devient cover, A perd son badge (1 seule cover par logement)</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Visuel</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>2 covers en même temps → bug</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr"/>
+      <c r="I241" s="3" t="inlineStr"/>
+      <c r="J241" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" ht="45" customHeight="1">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>13.4 Sous-onglet Photos (galerie)</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>13.4.10</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.documents.filter(d =&gt; d.parentType==='logement' &amp;&amp; d.category==='photos' &amp;&amp; d.isCover).length`</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>0 ou 1 (pas plus d'une cover)</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 1 → bug exclusivité</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr"/>
+      <c r="I242" s="3" t="inlineStr"/>
+      <c r="J242" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" ht="45" customHeight="1">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>13.5.1</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Connecter Drive + déposer manuellement un fichier dans ImmoTrack/&lt;ent&gt;/&lt;imm&gt;/&lt;log&gt;/📄 Documents/ via Drive web</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Fichier créé sur Drive</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Drive web</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>Pas d'accès écriture Drive</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr"/>
+      <c r="I243" s="3" t="inlineStr"/>
+      <c r="J243" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" ht="45" customHeight="1">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>13.5.2</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Sur l'app : aller sur fiche logement → ouvrir sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Après 200ms : toast '📥 1 fichier(s) Drive détecté(s)'</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>Pas de toast → scan ne s'est pas déclenché</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr"/>
+      <c r="I244" s="3" t="inlineStr"/>
+      <c r="J244" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" ht="32" customHeight="1">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>13.5.3</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.documents.filter(d =&gt; d._discoveredFromDrive)`</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Array contenant le fichier déposé manuellement</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>Array vide → merge KO</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr"/>
+      <c r="I245" s="3" t="inlineStr"/>
+      <c r="J245" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" ht="32" customHeight="1">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>13.5.4</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Ouvrir le fichier découvert dans l'app (clic 👁)</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Téléchargement depuis Drive (idbKey:null) + cache IDB + affichage</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Visuel + console</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>Erreur fetch Drive</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr"/>
+      <c r="I246" s="3" t="inlineStr"/>
+      <c r="J246" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" ht="32" customHeight="1">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>13.5.5</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Supprimer ce fichier dans Drive web (mettre à la corbeille)</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>Drive corbeille rempli</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>Drive web</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr"/>
+      <c r="I247" s="3" t="inlineStr"/>
+      <c r="J247" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" ht="32" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>13.5.6</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>App : F5 + ouvrir sous-onglet Documents</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>Toast '🗑 1 fichier(s) supprimé(s) côté Drive' + fichier disparaît de la liste</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>Toast + visuel</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>Fichier toujours visible → tombstone KO</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr"/>
+      <c r="I248" s="3" t="inlineStr"/>
+      <c r="J248" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" ht="45" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>13.5.7</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.documents.find(d =&gt; d._deletedBy === 'drive_web')`</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>Objet tombstone trouvé</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>null → flag non posé</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr"/>
+      <c r="I249" s="3" t="inlineStr"/>
+      <c r="J249" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" ht="32" customHeight="1">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>13.5 Drive lazy scan</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>13.5.8</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Throttle : ouvrir Documents puis Photos en moins de 30s</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>Scan une seule fois (skip 2e appel via throttle)</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Console (pas de toast 2x)</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>Toast 2x → throttle KO</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr"/>
+      <c r="I250" s="3" t="inlineStr"/>
+      <c r="J250" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" ht="32" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>13.6 Sync Drive payload (audit fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>13.6.1</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Ajouter PJ sur mvt global SCI (qui = 'SCI:nom')</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>PJ créée en IDB local (driveFileId null car logRef='SCI:nom')</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>Erreur upload</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr"/>
+      <c r="I251" s="3" t="inlineStr"/>
+      <c r="J251" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" ht="45" customHeight="1">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>13.6 Sync Drive payload (audit fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>13.6.2</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Console : `_buildEntityPayload(DB.entites[0]).documents.length`</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>Inclut les docs de mouvements de cette entité (même globaux SCI)</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>Documents manquants → fix #1 v15.03 régression</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr"/>
+      <c r="I252" s="3" t="inlineStr"/>
+      <c r="J252" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" ht="45" customHeight="1">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>13.6 Sync Drive payload (audit fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>13.6.3</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Forcer push Drive → vérifier que entity-*.json contient documents[]</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>Documents bien dans le JSON serialisé</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Drive web → ouvrir JSON</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>documents[] vide ou absent</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr"/>
+      <c r="I253" s="3" t="inlineStr"/>
+      <c r="J253" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" ht="32" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>13.6 Sync Drive payload (audit fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>13.6.4</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Sur 2e device (ou Reset DB) → pull</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>Documents repris correctement</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>Console + UI</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>Documents perdus → sync incomplet</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr"/>
+      <c r="I254" s="3" t="inlineStr"/>
+      <c r="J254" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" ht="32" customHeight="1">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>13.7 Audit-trail del&lt;X&gt; (fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>13.7.1</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Supprimer un mouvement avec PJ</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>Confirm + toast suppression OK</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>Crash</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr"/>
+      <c r="I255" s="3" t="inlineStr"/>
+      <c r="J255" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" ht="45" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>13.7 Audit-trail del&lt;X&gt; (fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>13.7.2</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Console : `DB.auditTrail.filter(e =&gt; e.action==='delete' &amp;&amp; e.entityType==='mouvement').slice(-1)[0]`</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Entry présent avec ts récent</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>undefined → delMv pas hooké</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr"/>
+      <c r="I256" s="3" t="inlineStr"/>
+      <c r="J256" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" ht="45" customHeight="1">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>13.7 Audit-trail del&lt;X&gt; (fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>13.7.3</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Tester suppressions delQuit / delAss / delMrh / delEDL / delImm</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>Chaque suppression crée une entrée audit-trail (action='delete')</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>Console : `[...new Set(DB.auditTrail.filter(e =&gt; e.action==='delete').map(e =&gt; e.entityType))]`</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>Array &lt; 6 types couverts → hooks manquants</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr"/>
+      <c r="I257" s="3" t="inlineStr"/>
+      <c r="J257" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" ht="32" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>13.8 Cas limites / edge cases</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>13.8.1</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>Reset DB local → pull Drive</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>PJ idbKey:null après pull (binaire pas en IDB local)</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>Erreur pull</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr"/>
+      <c r="I258" s="3" t="inlineStr"/>
+      <c r="J258" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" ht="32" customHeight="1">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>13.8 Cas limites / edge cases</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>13.8.2</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer 👁 sur PJ avec idbKey:null + driveFileId:non-null</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>Toast '📥 Téléchargement depuis Drive…' puis ouverture</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>Toast + visuel</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>Erreur 'Binaire introuvable'</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="inlineStr"/>
+      <c r="I259" s="3" t="inlineStr"/>
+      <c r="J259" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" ht="32" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>13.8 Cas limites / edge cases</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>13.8.3</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>Cliquer 👁 sur PJ idbKey:null + driveFileId:null (orphelin)</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>Toast erreur 'Binaire PJ introuvable (IDB + Drive)'</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>Crash JS</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr"/>
+      <c r="I260" s="3" t="inlineStr"/>
+      <c r="J260" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" ht="32" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>13.8 Cas limites / edge cases</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>13.8.4</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>Console : `window._attachmentOrphans(DB.documents).length`</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>Compteur de PJ orphelines (idéalement 0)</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr"/>
+      <c r="I261" s="3" t="inlineStr"/>
+      <c r="J261" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" ht="32" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>13.8 Cas limites / edge cases</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>13.8.5</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>Drive non connecté : ajouter PJ</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>PJ stockée en IDB local uniquement, driveFileId reste null</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>Upload tenté → erreur OAuth</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr"/>
+      <c r="I262" s="3" t="inlineStr"/>
+      <c r="J262" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" ht="45" customHeight="1">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>13.8 Cas limites / edge cases</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>13.8.6</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Reconnecter Drive : vérifier que les PJ orphelines (driveFileId:null) ne re-uploadent PAS automatiquement</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Pas de re-upload auto (limite V1, à implémenter V1.1)</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>Console + Drive web</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>Re-upload tenté à chaque connexion (gaspillage API)</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="inlineStr"/>
+      <c r="I263" s="3" t="inlineStr"/>
+      <c r="J263" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A201:J201"/>
     <mergeCell ref="A173:J173"/>
     <mergeCell ref="A204:J204"/>
     <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A215:J215"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A148:J148"/>
     <mergeCell ref="A209:J209"/>
@@ -9168,7 +11192,7 @@
     <mergeCell ref="A165:J165"/>
     <mergeCell ref="A161:J161"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:J214">
+  <conditionalFormatting sqref="A2:J263">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="✅"</formula>
     </cfRule>
@@ -9183,7 +11207,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H214" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Statut invalide" error="Choisir : ✅ OK | ❌ KO | ⏭️ Skip | ⚠️ Partiel" promptTitle="Statut" prompt="✅ OK ❌ KO ⏭️ Skip ⚠️ Partiel" type="list">
+    <dataValidation sqref="H2:H263" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Statut invalide" error="Choisir : ✅ OK | ❌ KO | ⏭️ Skip | ⚠️ Partiel" promptTitle="Statut" prompt="✅ OK ❌ KO ⏭️ Skip ⚠️ Partiel" type="list">
       <formula1>"✅,❌,⏭️,⚠️"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9197,7 +11221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9213,7 +11237,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>SYNTHÈSE VALIDATION V1 COMMERCIALE ImmoTrack v14.98</t>
+          <t>SYNTHÈSE VALIDATION V1 COMMERCIALE ImmoTrack v15.03</t>
         </is>
       </c>
     </row>
@@ -9231,7 +11255,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA(Checklist!C2:C214)</f>
+        <f>COUNTA(Checklist!C2:C263)</f>
         <v/>
       </c>
     </row>
@@ -9242,7 +11266,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>COUNTIF(Checklist!H2:H214, "✅")</f>
+        <f>COUNTIF(Checklist!H2:H263, "✅")</f>
         <v/>
       </c>
     </row>
@@ -9253,7 +11277,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>COUNTIF(Checklist!H2:H214, "❌")</f>
+        <f>COUNTIF(Checklist!H2:H263, "❌")</f>
         <v/>
       </c>
     </row>
@@ -9264,7 +11288,7 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>COUNTIF(Checklist!H2:H214, "⚠️")</f>
+        <f>COUNTIF(Checklist!H2:H263, "⚠️")</f>
         <v/>
       </c>
     </row>
@@ -9275,7 +11299,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Checklist!H2:H214, "⏭️")</f>
+        <f>COUNTIF(Checklist!H2:H263, "⏭️")</f>
         <v/>
       </c>
     </row>
@@ -9767,6 +11791,41 @@
       </c>
       <c r="H25" s="13">
         <f>IF(B25=0,0,(C25+E25+F25)/B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>13. PJ UNIFIÉES</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>COUNTIF(Checklist!A:A, "13. PJ UNIFIÉES")</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>COUNTIFS(Checklist!A:A, "13. PJ UNIFIÉES", Checklist!H:H, "✅")</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>COUNTIFS(Checklist!A:A, "13. PJ UNIFIÉES", Checklist!H:H, "❌")</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>COUNTIFS(Checklist!A:A, "13. PJ UNIFIÉES", Checklist!H:H, "⚠️")</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>COUNTIFS(Checklist!A:A, "13. PJ UNIFIÉES", Checklist!H:H, "⏭️")</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>B26-C26-D26-E26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>IF(B26=0,0,(C26+E26+F26)/B26)</f>
         <v/>
       </c>
     </row>
@@ -9784,7 +11843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10498,6 +12557,278 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Vérif zéro PJ legacy non migrée</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>DB.mouvements.filter(m =&gt; m.pj &amp;&amp; m.pj.dataB64).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Compter PJ mouvements migrées</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>DB.documents.filter(d =&gt; d.parentType==="mouvement" &amp;&amp; !d._deleted).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="50" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Compter photos logements</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>DB.documents.filter(d =&gt; d.parentType==="logement" &amp;&amp; d.category==="photos" &amp;&amp; !d._deleted).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Compter docs découverts Drive</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>DB.documents.filter(d =&gt; d._discoveredFromDrive &amp;&amp; !d._deleted).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Trouver orphelins (ni IDB ni Drive)</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>window._attachmentOrphans(DB.documents)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Documents avec cover marquée</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>DB.documents.filter(d =&gt; d.isCover &amp;&amp; !d._deleted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Documents avec driveFileId non-null</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>DB.documents.filter(d =&gt; d.driveFileId &amp;&amp; !d._deleted).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Documents avec idbKey local</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>DB.documents.filter(d =&gt; d.idbKey &amp;&amp; !d._deleted).length</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Forcer une migration legacy manuelle</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>_migratePjMouvementsToAttachments()</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="50" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PJ</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Test save attachment programmatique (logement)</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>_attachmentSaveForEntity({type:"logement",id:1,ref:"F-001",logRef:"F-001",category:"documents"}, {name:"test.pdf",mime:"application/pdf",size:100,dataB64:"data:application/pdf;base64,JVBERi0xLjQK"})</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE DRIVE-SCAN</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>Forcer scan manuel d'un logement</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>_drvLazyScanLogement("F-001", ["documents","photos"])</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE DRIVE-SCAN</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>Reset throttle scan (debug)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>Object.keys(window).filter(k =&gt; k.startsWith("__drvLastScan_")).forEach(k =&gt; delete window[k])</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE DRIVE-SCAN</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Liste fichiers d'un dossier Drive</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>_drvListFolderFiles(DB.logements[0].driveFolders.documents)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>CONSOLE PAYLOAD</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Vérif payload entité contient documents (fix v15.03)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>_buildEntityPayload(DB.entites[0]).documents.length</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>AUDIT v15.03</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Vérif hooks audit-trail sur del&lt;X&gt; (6 fns)</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>["delImm","delMv","delQuit","delAss","delMrh","delEDL"].forEach(fn =&gt; console.log(fn, "audit:", (window[fn]?.toString()||"").includes("_auditLog") ? "✅" : "❌"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>AUDIT v15.03</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Compter types entityType dans audit-trail</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>[...new Set(DB.auditTrail.map(e =&gt; e.entityType))]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
